--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1897,6 +1897,907 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131736079</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>664895</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7074001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131736469</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>664902</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7073950</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131736468</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>664818</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7074027</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131738061</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>664799</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7073959</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131734943</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>664862</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7074006</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131735804</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91362</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>664914</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7073929</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131736078</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>664821</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7074031</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131734253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91956</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>664882</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7073991</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131734252</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91956</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rödtjärnen Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>664940</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7073929</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R16" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>80365</v>
+        <v>57895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R17" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R16" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B17" t="n">
-        <v>57895</v>
+        <v>80366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R17" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91362</v>
+        <v>91363</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91956</v>
+        <v>91957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91956</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R16" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>80366</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R17" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91363</v>
+        <v>91366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91957</v>
+        <v>91960</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>91960</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R16" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R17" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R16" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>80369</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R17" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91366</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91960</v>
+        <v>91966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91960</v>
+        <v>91966</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91966</v>
+        <v>91969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91966</v>
+        <v>91969</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B16" t="n">
-        <v>80374</v>
+        <v>57909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R16" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>80379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R17" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91969</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91969</v>
+        <v>91974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>131736468</v>
       </c>
       <c r="B16" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>131738061</v>
       </c>
       <c r="B17" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91380</v>
+        <v>91382</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91974</v>
+        <v>91976</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91974</v>
+        <v>91976</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>80381</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R16" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>80381</v>
+        <v>57911</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R17" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B16" t="n">
-        <v>80381</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R16" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B17" t="n">
-        <v>57911</v>
+        <v>80381</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R17" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>131736469</v>
       </c>
       <c r="B15" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B16" t="n">
-        <v>57911</v>
+        <v>80415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R16" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B17" t="n">
-        <v>80381</v>
+        <v>57945</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R17" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91382</v>
+        <v>91418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>91976</v>
+        <v>92012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>91976</v>
+        <v>92012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41454-2024 artfynd.xlsx
+++ b/artfynd/A 41454-2024 artfynd.xlsx
@@ -1902,7 +1902,7 @@
         <v>131736079</v>
       </c>
       <c r="B14" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131738061</v>
+        <v>131736468</v>
       </c>
       <c r="B16" t="n">
-        <v>80420</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,21 +2108,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>664799</v>
+        <v>664818</v>
       </c>
       <c r="R16" t="n">
-        <v>7073959</v>
+        <v>7074027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2198,10 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131736468</v>
+        <v>131738061</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>80422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>664818</v>
+        <v>664799</v>
       </c>
       <c r="R17" t="n">
-        <v>7074027</v>
+        <v>7073959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>131734943</v>
       </c>
       <c r="B18" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>131735804</v>
       </c>
       <c r="B19" t="n">
-        <v>91423</v>
+        <v>91426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>131736078</v>
       </c>
       <c r="B20" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>131734253</v>
       </c>
       <c r="B21" t="n">
-        <v>92017</v>
+        <v>92020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>131734252</v>
       </c>
       <c r="B22" t="n">
-        <v>92017</v>
+        <v>92020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
